--- a/reference_keys/KEY_PlayInterventionTraining_4.xlsx
+++ b/reference_keys/KEY_PlayInterventionTraining_4.xlsx
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
